--- a/在老谭投资表.xlsx
+++ b/在老谭投资表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/didi/Desktop/投资/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1592C9BC-C361-8544-B364-0C24617ADEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6EDF46-4CD6-8847-B34C-2146EB89CBF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="800" windowWidth="30240" windowHeight="17980" xr2:uid="{23611AF4-1D92-9447-8861-7FBE08848BE4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$66</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="25">
   <si>
     <t>投资金额</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -409,10 +409,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$E$71:$E$85</c:f>
+              <c:f>Sheet1!$E$71:$E$86</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>45689</c:v>
                 </c:pt>
@@ -458,15 +458,18 @@
                 <c:pt idx="14">
                   <c:v>46113</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46143</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$71:$F$85</c:f>
+              <c:f>Sheet1!$F$71:$F$86</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>6200</c:v>
                 </c:pt>
@@ -511,6 +514,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>25200</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>11300</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1214,15 +1220,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>225108</xdr:colOff>
+      <xdr:colOff>466408</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:rowOff>69850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>352743</xdr:colOff>
+      <xdr:colOff>594043</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3857,14 +3863,14 @@
       </c>
       <c r="H58" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="J58" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" hidden="1">
       <c r="A59" s="2">
         <v>46095</v>
       </c>
@@ -3881,17 +3887,29 @@
         <f t="shared" si="5"/>
         <v>46130</v>
       </c>
+      <c r="F59" s="2">
+        <v>46157</v>
+      </c>
       <c r="G59" s="1">
         <f t="shared" si="6"/>
         <v>8400</v>
       </c>
-      <c r="H59" s="1">
+      <c r="H59" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>-24</v>
+        <v/>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="J59" s="1" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2026-05</v>
+      </c>
+      <c r="K59" s="1">
+        <v>8400</v>
+      </c>
+      <c r="L59" s="1">
+        <v>200</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -3917,7 +3935,7 @@
       </c>
       <c r="H60" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3943,7 +3961,7 @@
       </c>
       <c r="H61" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -3969,7 +3987,7 @@
       </c>
       <c r="H62" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -3995,7 +4013,7 @@
       </c>
       <c r="H63" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M63" s="1" t="s">
         <v>22</v>
@@ -4024,7 +4042,7 @@
       </c>
       <c r="H64" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -4050,7 +4068,7 @@
       </c>
       <c r="H65" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -4076,7 +4094,7 @@
       </c>
       <c r="H66" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>24</v>
@@ -4094,7 +4112,7 @@
       </c>
       <c r="C70" s="4">
         <f>SUMIF(I:I,"",B:B)</f>
-        <v>2350000</v>
+        <v>2050000</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>16</v>
@@ -4109,7 +4127,7 @@
       </c>
       <c r="C71" s="4">
         <f>SUM(K:K)</f>
-        <v>283790</v>
+        <v>292190</v>
       </c>
       <c r="E71" s="6">
         <v>45689</v>
@@ -4125,7 +4143,7 @@
       </c>
       <c r="C72" s="4">
         <f>SUMIF(I:I,"",G:G)</f>
-        <v>65800</v>
+        <v>57400</v>
       </c>
       <c r="E72" s="6">
         <v>45717</v>
@@ -4258,7 +4276,7 @@
       </c>
       <c r="F86" s="7">
         <f t="shared" si="8"/>
-        <v>2900</v>
+        <v>11300</v>
       </c>
     </row>
     <row r="87" spans="5:6">
@@ -4283,7 +4301,7 @@
       <c r="F93" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L64" xr:uid="{E9A602FF-479D-CC4C-BDFA-E609B00DE0B1}">
+  <autoFilter ref="A1:L66" xr:uid="{E9A602FF-479D-CC4C-BDFA-E609B00DE0B1}">
     <filterColumn colId="8">
       <filters blank="1"/>
     </filterColumn>
